--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:03:47+00:00</t>
+    <t>2023-10-16T13:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:05:21+00:00</t>
+    <t>2023-10-16T13:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:49:57+00:00</t>
+    <t>2023-10-23T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -602,7 +602,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-practitioner-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-practitioner-identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -944,7 +944,7 @@
     <t>Practitioner.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
 </t>
   </si>
   <si>
@@ -972,7 +972,7 @@
     <t>Practitioner.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
@@ -1013,7 +1013,7 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type}
 </t>
   </si>
   <si>
@@ -1151,7 +1151,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
 </t>
   </si>
   <si>
@@ -2220,7 +2220,7 @@
     <col min="8" max="8" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="82.08984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="83.046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T09:15:45+00:00</t>
+    <t>2023-10-23T11:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:28:06+00:00</t>
+    <t>2023-11-06T10:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T09:05:25+00:00</t>
+    <t>2023-11-08T15:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T15:11:22+00:00</t>
+    <t>2023-11-21T10:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -425,7 +425,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -445,7 +445,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -1281,7 +1281,7 @@
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T10:12:39+00:00</t>
+    <t>2023-12-04T10:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T10:06:25+00:00</t>
+    <t>2023-12-04T12:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:30:51+00:00</t>
+    <t>2023-12-04T12:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:19:21+00:00</t>
+    <t>2023-12-11T10:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T10:12:17+00:00</t>
+    <t>2024-02-05T11:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -728,7 +728,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-practitioner-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2034" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T13:27:08+00:00</t>
+    <t>2024-02-12T14:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -662,6 +662,13 @@
   </si>
   <si>
     <t>Often, specific identities are assigned for the agent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:system}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the identifier.system pattern</t>
   </si>
   <si>
     <t>PRD-7 (or XCN.1)</t>
@@ -1044,6 +1051,155 @@
   </si>
   <si>
     <t>./IdentifierIssuingAuthority</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs</t>
+  </si>
+  <si>
+    <t>idNatPs</t>
+  </si>
+  <si>
+    <t>Identifiant national des PS. Cet identifiant est notamment utilisé dans le cadre du DMP et de la CPS. Cet identifiant est préfixé selon source de provenance de l'identifiant (cf Annexe Transverse – Source des données métier pour les professionnels et les structures du CI-SIS.)</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.use</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.type</t>
+  </si>
+  <si>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;code value="IDNPS"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.system</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.71.4.2.1</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.value</t>
+  </si>
+  <si>
+    <t>Identifiant national de la personne physique. 0 + ADELI ou 8 + RPPSidPP,
+ Personne/Identifiant PP si l’instance correspond à un identifiant RPPS ou ADELI, sinon Personne/identification nationale PP.</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.period</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:idNatPs.assigner</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps</t>
+  </si>
+  <si>
+    <t>rpps</t>
+  </si>
+  <si>
+    <t>Numéro RPPS (11 chiffres)</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.use</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;code value="RPPS"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.system</t>
+  </si>
+  <si>
+    <t>http://rpps.esante.gouv.fr</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.value</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.period</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:rpps.assigner</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:adeli</t>
+  </si>
+  <si>
+    <t>adeli</t>
+  </si>
+  <si>
+    <t>Numéro ADELI (9 chiffres)</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:adeli.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:adeli.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:adeli.use</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:adeli.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;code value="ADELI"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:adeli.system</t>
+  </si>
+  <si>
+    <t>http://adeli.esante.gouv.fr</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:adeli.value</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:adeli.period</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:adeli.assigner</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -1696,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AN82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.38671875" customWidth="true" bestFit="true"/>
@@ -3987,16 +4143,16 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>203</v>
@@ -4014,24 +4170,24 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4140,10 +4296,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4254,10 +4410,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4283,16 +4439,16 @@
         <v>172</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4317,13 +4473,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4341,7 +4497,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4359,7 +4515,7 @@
         <v>102</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4370,10 +4526,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4396,19 +4552,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4437,7 +4593,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4455,7 +4611,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4470,10 +4626,10 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4484,10 +4640,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4596,10 +4752,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4710,10 +4866,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4739,16 +4895,16 @@
         <v>148</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4797,7 +4953,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4812,10 +4968,10 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4826,10 +4982,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4938,10 +5094,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5052,10 +5208,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5081,16 +5237,16 @@
         <v>132</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5103,7 +5259,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5139,7 +5295,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5154,10 +5310,10 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5168,10 +5324,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5197,13 +5353,13 @@
         <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5253,7 +5409,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5268,10 +5424,10 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5282,10 +5438,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5311,16 +5467,16 @@
         <v>172</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5369,7 +5525,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5384,10 +5540,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5398,10 +5554,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5427,16 +5583,16 @@
         <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5485,7 +5641,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5500,10 +5656,10 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5514,10 +5670,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5540,19 +5696,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5601,7 +5757,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5616,10 +5772,10 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5630,10 +5786,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5659,16 +5815,16 @@
         <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5717,7 +5873,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5732,10 +5888,10 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5746,10 +5902,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5775,16 +5931,16 @@
         <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5797,7 +5953,7 @@
         <v>77</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>77</v>
@@ -5833,7 +5989,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5848,13 +6004,13 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5862,10 +6018,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5891,13 +6047,13 @@
         <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5911,7 +6067,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -5947,7 +6103,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5962,13 +6118,13 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5976,10 +6132,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6002,16 +6158,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6061,7 +6217,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6073,16 +6229,16 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6090,10 +6246,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6116,16 +6272,16 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6175,7 +6331,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6187,16 +6343,16 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6204,12 +6360,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6230,26 +6388,22 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>336</v>
+        <v>207</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q40" t="s" s="2">
-        <v>337</v>
-      </c>
+      <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6293,13 +6447,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>203</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>100</v>
@@ -6308,24 +6462,24 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>338</v>
+        <v>211</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>339</v>
+        <v>213</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>214</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6336,7 +6490,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6348,20 +6502,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>341</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>342</v>
+        <v>105</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6409,28 +6559,28 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>340</v>
+        <v>107</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>346</v>
+        <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>347</v>
+        <v>108</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>348</v>
+        <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6438,14 +6588,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6464,20 +6614,18 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>350</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>112</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
+        <v>113</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6513,19 +6661,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>349</v>
+        <v>118</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6537,16 +6685,16 @@
         <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>355</v>
+        <v>119</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>357</v>
+        <v>102</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6554,10 +6702,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>216</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6568,31 +6716,31 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>360</v>
+        <v>172</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>361</v>
+        <v>217</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>362</v>
+        <v>218</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>363</v>
+        <v>219</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>364</v>
+        <v>220</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6617,13 +6765,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6641,13 +6789,13 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>359</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>100</v>
@@ -6656,13 +6804,13 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>365</v>
+        <v>102</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>366</v>
+        <v>225</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>367</v>
+        <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6670,10 +6818,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>368</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6696,19 +6844,19 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>370</v>
+        <v>229</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>371</v>
+        <v>231</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6718,7 +6866,7 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>77</v>
@@ -6733,13 +6881,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>219</v>
+        <v>152</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6757,7 +6905,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>368</v>
+        <v>233</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6772,13 +6920,13 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>374</v>
+        <v>234</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>375</v>
+        <v>225</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6786,10 +6934,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>295</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6812,17 +6960,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>378</v>
+        <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>379</v>
+        <v>296</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O45" t="s" s="2">
-        <v>381</v>
+        <v>299</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6832,10 +6982,10 @@
         <v>77</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>77</v>
+        <v>347</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>77</v>
+        <v>300</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>77</v>
@@ -6871,7 +7021,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>377</v>
+        <v>301</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6886,13 +7036,13 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>382</v>
+        <v>302</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>383</v>
+        <v>303</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>384</v>
+        <v>304</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6900,10 +7050,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>305</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6914,7 +7064,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6923,23 +7073,21 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>386</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>387</v>
+        <v>349</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>388</v>
+        <v>307</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -6951,7 +7099,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -6987,28 +7135,28 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>310</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>391</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>392</v>
+        <v>311</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>393</v>
+        <v>312</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>394</v>
+        <v>313</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7016,10 +7164,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>395</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>395</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7030,7 +7178,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -7039,18 +7187,20 @@
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>396</v>
+        <v>315</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>397</v>
+        <v>316</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7099,28 +7249,28 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>395</v>
+        <v>319</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>320</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>399</v>
+        <v>321</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>400</v>
+        <v>322</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>401</v>
+        <v>323</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7128,10 +7278,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>402</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>402</v>
+        <v>324</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7151,18 +7301,20 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>104</v>
+        <v>325</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>105</v>
+        <v>326</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7211,7 +7363,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>107</v>
+        <v>329</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7220,19 +7372,19 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>77</v>
+        <v>330</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>108</v>
+        <v>332</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>77</v>
+        <v>333</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7240,14 +7392,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7263,21 +7417,21 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>112</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7313,19 +7467,19 @@
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>118</v>
+        <v>203</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7337,63 +7491,59 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>102</v>
+        <v>211</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>214</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>405</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>105</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7441,25 +7591,25 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>408</v>
+        <v>107</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7470,14 +7620,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>215</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7496,18 +7646,18 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>410</v>
+        <v>112</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7543,19 +7693,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>118</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7567,16 +7717,16 @@
         <v>100</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>413</v>
+        <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>102</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7584,10 +7734,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7595,7 +7745,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>88</v>
@@ -7604,24 +7754,26 @@
         <v>77</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7645,11 +7797,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>420</v>
+        <v>223</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7667,10 +7821,10 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>224</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>88</v>
@@ -7682,13 +7836,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>421</v>
+        <v>102</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>400</v>
+        <v>225</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>422</v>
+        <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7696,10 +7850,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>226</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7719,22 +7873,22 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>313</v>
+        <v>227</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>424</v>
+        <v>228</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>425</v>
+        <v>229</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>316</v>
+        <v>230</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>426</v>
+        <v>231</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7744,7 +7898,7 @@
         <v>77</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>77</v>
@@ -7759,13 +7913,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>77</v>
+        <v>344</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7783,7 +7937,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>423</v>
+        <v>233</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7795,16 +7949,16 @@
         <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>318</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>427</v>
+        <v>234</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>428</v>
+        <v>225</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>429</v>
+        <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7812,10 +7966,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>430</v>
+        <v>295</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7835,21 +7989,23 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>323</v>
+        <v>132</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>431</v>
+        <v>296</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>432</v>
+        <v>346</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7858,10 +8014,10 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>77</v>
+        <v>300</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -7897,7 +8053,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>430</v>
+        <v>301</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7909,16 +8065,16 @@
         <v>100</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>328</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>77</v>
+        <v>302</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>434</v>
+        <v>303</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7926,10 +8082,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>435</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>435</v>
+        <v>305</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7940,7 +8096,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -7949,23 +8105,21 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>436</v>
+        <v>306</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>437</v>
+        <v>307</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -7977,7 +8131,7 @@
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -7989,13 +8143,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8013,13 +8167,13 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>435</v>
+        <v>310</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>100</v>
@@ -8028,15 +8182,3113 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q67" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="R67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AN73" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="B74" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K74" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="L74" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y79" s="2"/>
+      <c r="Z79" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:02:40+00:00</t>
+    <t>2024-02-26T11:03:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:03:57+00:00</t>
+    <t>2024-03-04T10:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T10:55:37+00:00</t>
+    <t>2024-03-11T09:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T09:42:54+00:00</t>
+    <t>2024-03-11T10:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T10:34:02+00:00</t>
+    <t>2024-03-20T14:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/main/StructureDefinition-fr-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="494">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:49:36+00:00</t>
+    <t>2024-03-21T08:11:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,6 +630,23 @@
   </si>
   <si>
     <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.extension:specialty</t>
+  </si>
+  <si>
+    <t>specialty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-specialty}
+</t>
+  </si>
+  <si>
+    <t>FR Core Practitioner Specialty Extension</t>
+  </si>
+  <si>
+    <t>This extension adds the element "specialty" to the FHIR Practitioner resource.
+http://esante.gouv.fr/sites/NOS/TABS/TRE_R38-SpecialiteOrdinale.tabs</t>
   </si>
   <si>
     <t>Practitioner.modifierExtension</t>
@@ -1852,7 +1869,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN82"/>
+  <dimension ref="A1:AN83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.38671875" customWidth="true" bestFit="true"/>
@@ -1865,7 +1882,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.65234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.90625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3957,43 +3974,41 @@
         <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -4029,19 +4044,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4059,7 +4074,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4077,7 +4092,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4090,23 +4105,25 @@
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -4143,10 +4160,10 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>208</v>
+        <v>115</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>209</v>
+        <v>116</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
@@ -4155,7 +4172,7 @@
         <v>117</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4167,27 +4184,27 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>102</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4198,7 +4215,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4207,19 +4224,21 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>105</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4255,62 +4274,62 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4322,17 +4341,15 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4369,37 +4386,37 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4410,46 +4427,44 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4473,49 +4488,49 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4526,10 +4541,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4546,25 +4561,25 @@
         <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4589,11 +4604,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4611,7 +4628,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4626,10 +4643,10 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4640,10 +4657,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4663,19 +4680,23 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4699,13 +4720,11 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4723,7 +4742,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4732,16 +4751,16 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>108</v>
+        <v>230</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4752,21 +4771,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4778,17 +4797,15 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4825,37 +4842,37 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4866,14 +4883,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4889,23 +4906,21 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>113</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4941,19 +4956,19 @@
         <v>77</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>118</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4965,13 +4980,13 @@
         <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>244</v>
+        <v>102</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4982,10 +4997,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4996,7 +5011,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -5005,19 +5020,23 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>105</v>
+        <v>243</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -5065,25 +5084,25 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5094,21 +5113,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -5120,17 +5139,15 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5167,37 +5184,37 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5208,21 +5225,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5231,23 +5248,21 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>248</v>
+        <v>112</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>249</v>
+        <v>113</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5259,7 +5274,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5283,37 +5298,37 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5324,10 +5339,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5350,18 +5365,20 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5373,7 +5390,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5409,7 +5426,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5424,10 +5441,10 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5438,10 +5455,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5464,20 +5481,18 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5525,7 +5540,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5540,10 +5555,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5554,10 +5569,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5580,19 +5595,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5641,7 +5656,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5656,10 +5671,10 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5670,10 +5685,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5696,19 +5711,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5757,7 +5772,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5772,10 +5787,10 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5786,10 +5801,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5812,19 +5827,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>284</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5873,7 +5888,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5888,10 +5903,10 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5902,10 +5917,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5913,7 +5928,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -5928,19 +5943,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5953,7 +5968,7 @@
         <v>77</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>77</v>
@@ -5989,7 +6004,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6004,13 +6019,13 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6018,10 +6033,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6044,18 +6059,20 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -6067,7 +6084,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6103,7 +6120,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6118,13 +6135,13 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6132,10 +6149,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6143,7 +6160,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -6158,16 +6175,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>315</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6181,7 +6198,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6217,7 +6234,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6229,16 +6246,16 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6246,10 +6263,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6272,16 +6289,16 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6331,7 +6348,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6343,16 +6360,16 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6360,14 +6377,12 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6388,18 +6403,18 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6447,41 +6462,43 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>203</v>
+        <v>334</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>210</v>
+        <v>336</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>212</v>
+        <v>338</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6499,19 +6516,21 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>105</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6559,50 +6578,50 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6614,17 +6633,15 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6661,37 +6678,37 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6702,46 +6719,44 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6765,49 +6780,49 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6818,10 +6833,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6838,25 +6853,25 @@
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>341</v>
+        <v>222</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6866,7 +6881,7 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>77</v>
@@ -6881,13 +6896,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6905,7 +6920,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6920,10 +6935,10 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6937,7 +6952,7 @@
         <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6960,19 +6975,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>346</v>
+        <v>234</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6985,7 +7000,7 @@
         <v>347</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>77</v>
@@ -6997,13 +7012,13 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>77</v>
+        <v>348</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>349</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -7021,7 +7036,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7036,13 +7051,13 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7050,10 +7065,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7076,18 +7091,20 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7096,10 +7113,10 @@
         <v>77</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7135,7 +7152,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7150,13 +7167,13 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7164,10 +7181,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7190,16 +7207,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>315</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7213,7 +7230,7 @@
         <v>77</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>77</v>
@@ -7249,7 +7266,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7261,16 +7278,16 @@
         <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7278,10 +7295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7304,16 +7321,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7363,7 +7380,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7375,16 +7392,16 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7392,14 +7409,12 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7408,7 +7423,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7420,18 +7435,18 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7479,41 +7494,43 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>203</v>
+        <v>334</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>210</v>
+        <v>336</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>212</v>
+        <v>338</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7522,7 +7539,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7531,19 +7548,21 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>105</v>
+        <v>359</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7591,50 +7610,50 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7646,17 +7665,15 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7693,37 +7710,37 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7734,46 +7751,44 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7797,49 +7812,49 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7850,10 +7865,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7870,25 +7885,25 @@
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7898,7 +7913,7 @@
         <v>77</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>359</v>
+        <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>77</v>
@@ -7913,13 +7928,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7937,7 +7952,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7952,10 +7967,10 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7966,10 +7981,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7992,19 +8007,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>346</v>
+        <v>234</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8014,10 +8029,10 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8029,13 +8044,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>77</v>
+        <v>348</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>77</v>
+        <v>349</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8053,7 +8068,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8068,13 +8083,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8082,10 +8097,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8108,18 +8123,20 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8128,10 +8145,10 @@
         <v>77</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>77</v>
+        <v>366</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8167,7 +8184,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8182,13 +8199,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8196,10 +8213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8222,16 +8239,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>315</v>
+        <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8245,7 +8262,7 @@
         <v>77</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>77</v>
@@ -8281,7 +8298,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8293,16 +8310,16 @@
         <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8310,10 +8327,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8336,16 +8353,16 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8395,7 +8412,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8407,16 +8424,16 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8424,14 +8441,12 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8440,7 +8455,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8452,18 +8467,18 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8511,41 +8526,43 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>203</v>
+        <v>334</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>210</v>
+        <v>336</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>211</v>
+        <v>337</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>212</v>
+        <v>338</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8554,7 +8571,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8563,19 +8580,21 @@
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>105</v>
+        <v>372</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8623,50 +8642,50 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8678,17 +8697,15 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8725,37 +8742,37 @@
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8766,46 +8783,44 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
@@ -8829,49 +8844,49 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8882,10 +8897,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8902,25 +8917,25 @@
         <v>77</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8930,7 +8945,7 @@
         <v>77</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>77</v>
@@ -8945,13 +8960,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>152</v>
+        <v>226</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8969,7 +8984,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8984,10 +8999,10 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>234</v>
+        <v>102</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8998,10 +9013,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9024,19 +9039,19 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>346</v>
+        <v>234</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9046,10 +9061,10 @@
         <v>77</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9061,13 +9076,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>77</v>
+        <v>348</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>77</v>
+        <v>349</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9085,7 +9100,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9100,13 +9115,13 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9114,10 +9129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9140,18 +9155,20 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9160,10 +9177,10 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>77</v>
+        <v>379</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>77</v>
@@ -9199,7 +9216,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9214,13 +9231,13 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -9228,10 +9245,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9254,16 +9271,16 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>315</v>
+        <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9277,7 +9294,7 @@
         <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>77</v>
@@ -9313,7 +9330,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9325,16 +9342,16 @@
         <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9342,10 +9359,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9368,16 +9385,16 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9427,7 +9444,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9439,16 +9456,16 @@
         <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9456,10 +9473,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>378</v>
+        <v>329</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9482,26 +9499,22 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>279</v>
+        <v>330</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>379</v>
+        <v>331</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q67" t="s" s="2">
-        <v>383</v>
-      </c>
+      <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9545,7 +9558,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>378</v>
+        <v>334</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9557,27 +9570,27 @@
         <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>384</v>
+        <v>337</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9588,7 +9601,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9597,27 +9610,29 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O68" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9661,13 +9676,13 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>100</v>
@@ -9676,24 +9691,24 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>394</v>
+        <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>77</v>
+        <v>390</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9716,19 +9731,19 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9777,7 +9792,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9789,16 +9804,16 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>401</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9806,10 +9821,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9832,19 +9847,19 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9893,7 +9908,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9905,16 +9920,16 @@
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>406</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9922,10 +9937,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9936,7 +9951,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -9945,22 +9960,22 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>172</v>
+        <v>411</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9985,13 +10000,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>418</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>419</v>
+        <v>77</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10009,13 +10024,13 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>100</v>
@@ -10024,13 +10039,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10038,10 +10053,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10064,17 +10079,19 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>424</v>
+        <v>172</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10099,13 +10116,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>77</v>
+        <v>423</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>77</v>
+        <v>424</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10123,7 +10140,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10138,13 +10155,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -10152,10 +10169,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10166,7 +10183,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -10175,22 +10192,20 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10239,28 +10254,28 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>437</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10268,10 +10283,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10294,16 +10309,20 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10351,7 +10370,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10363,16 +10382,16 @@
         <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>442</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>77</v>
@@ -10380,10 +10399,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10394,7 +10413,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -10406,13 +10425,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>447</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>105</v>
+        <v>448</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>106</v>
+        <v>449</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10463,28 +10482,28 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>107</v>
+        <v>446</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>77</v>
+        <v>450</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>108</v>
+        <v>451</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>77</v>
+        <v>452</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
@@ -10492,21 +10511,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
@@ -10518,17 +10537,15 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10565,37 +10582,37 @@
         <v>77</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10606,14 +10623,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>451</v>
+        <v>110</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10626,26 +10643,24 @@
         <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>452</v>
+        <v>112</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>453</v>
+        <v>113</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O77" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
@@ -10681,19 +10696,19 @@
         <v>77</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>454</v>
+        <v>118</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10729,7 +10744,7 @@
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>77</v>
+        <v>456</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10742,23 +10757,25 @@
         <v>77</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O78" t="s" s="2">
-        <v>458</v>
+        <v>206</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10807,7 +10824,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10819,16 +10836,16 @@
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>459</v>
+        <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>460</v>
+        <v>102</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -10836,10 +10853,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10847,10 +10864,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10862,18 +10879,18 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -10897,11 +10914,13 @@
         <v>77</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>77</v>
@@ -10919,13 +10938,13 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>100</v>
@@ -10934,13 +10953,13 @@
         <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
@@ -10948,10 +10967,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10959,7 +10978,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>88</v>
@@ -10974,20 +10993,18 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>472</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -11011,13 +11028,11 @@
         <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>77</v>
+        <v>471</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>77</v>
@@ -11035,10 +11050,10 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>88</v>
@@ -11047,16 +11062,16 @@
         <v>100</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>320</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>
@@ -11064,10 +11079,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11090,18 +11105,20 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="O81" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
@@ -11149,7 +11166,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11161,16 +11178,16 @@
         <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>77</v>
+        <v>478</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>77</v>
@@ -11192,7 +11209,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
@@ -11204,7 +11221,7 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>227</v>
+        <v>330</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>482</v>
@@ -11215,9 +11232,7 @@
       <c r="N82" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="O82" t="s" s="2">
-        <v>485</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -11241,13 +11256,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -11271,24 +11286,140 @@
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK82" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AK83" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>77</v>
       </c>
     </row>
